--- a/GeoLibre-Web/analysis/yilan-public-facility-hazard-exposure-2026-09-26-update/result.xlsx
+++ b/GeoLibre-Web/analysis/yilan-public-facility-hazard-exposure-2026-09-26-update/result.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分析結果" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="統計摘要" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分析參數" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料來源" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部291處設施" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="分析結果" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="統計摘要" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="分析參數" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="資料來源" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="全部291處設施" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'分析結果'!$A$1:$T$172</definedName>
@@ -27,16 +27,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -47,7 +44,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -55,21 +52,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,102 +449,102 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>設施編號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>設施名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>設施類型</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>經度</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>緯度</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>source_month</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>點位說明</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>TWD97東向座標</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>TWD97北向座標</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>image_pixel_x</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>image_pixel_y</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>圖面覆蓋狀態</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>新版圖面分類</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>影像判讀狀態</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>距最近中高潛勢圖色_公尺</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>最近中高潛勢級別</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>300公尺內中高潛勢候選</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>篩選說明</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>sampled_rgb_class_pixels_5x5</t>
         </is>
@@ -14605,17 +14593,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>統計項目</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>數量</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>說明</t>
         </is>
@@ -14776,12 +14764,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>參數</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>設定</t>
         </is>
@@ -14896,37 +14884,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>圖層／資料</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>提供單位</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>來源網址</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>資料版次／期間</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>取得日期</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>分析用途</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>限制</t>
         </is>
@@ -15303,102 +15291,102 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>設施編號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>設施名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>設施類型</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>經度</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>緯度</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>source_month</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>點位說明</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>TWD97東向座標</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>TWD97北向座標</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>image_pixel_x</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>image_pixel_y</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>圖面覆蓋狀態</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>新版圖面分類</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>影像判讀狀態</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>距最近中高潛勢圖色_公尺</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>最近中高潛勢級別</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>300公尺內中高潛勢候選</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>篩選說明</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>sampled_rgb_class_pixels_5x5</t>
         </is>

--- a/GeoLibre-Web/analysis/yilan-public-facility-hazard-exposure-2026-09-26-update/result.xlsx
+++ b/GeoLibre-Web/analysis/yilan-public-facility-hazard-exposure-2026-09-26-update/result.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'分析結果'!$A$1:$T$172</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'統計摘要'!$A$1:$C$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'分析參數'!$A$1:$B$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資料來源'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資料來源'!$A$1:$I$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'全部291處設施'!$A$1:$T$292</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -14871,16 +14871,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14911,10 +14913,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>座標系統</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>本案角色</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>分析用途</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>限制</t>
         </is>
@@ -14948,10 +14960,20 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>圖面TWD97/TM2 121分帶（EPSG:3826）；PNG本身無座標標籤，由格網配準</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>本次主要官方圖資</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>新版液化潛勢地圖影像，按官方TWD97格網配準後作顯示與顏色分類。</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>此公開介面為PNG/WMTS影像，非本分析可下載的同版向量polygon；本成果為影像篩選。</t>
         </is>
@@ -14985,10 +15007,20 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>原始121分帶EPSG:3826；代表點輸出EPSG:4326</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>本次設施點來源（官方資料衍生）</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>133所學校的校地代表點。</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>representative point不是校門、校舍或校地界址。</t>
         </is>
@@ -15022,10 +15054,20 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>經緯度EPSG:4326（本案使用座標）</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>本次設施點來源（官方資料）</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>42個名稱屬醫院、衛生所或衛生室的點位。</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>不代表完整診所名冊。</t>
         </is>
@@ -15059,10 +15101,20 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>經緯度EPSG:4326（本案使用座標）</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>本次設施點來源（官方熱點資料作機關代理）</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>98個政府機關位置代理點。</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>只涵蓋設有熱點且名稱符合條件者，不是完整機關名冊。</t>
         </is>
@@ -15096,10 +15148,20 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>欄名TWD97；座標數值按經緯度EPSG:4326解讀</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>本次設施點來源（官方資料）</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>18個名稱包含分隊的消防設施點。</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>此版座標欄位名稱寫TWD97，但數值範圍為經緯度；按既有欄位稽核結果以EPSG:4326解讀。</t>
         </is>
@@ -15133,10 +15195,20 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>原始行政界EPSG:3826；地圖輸出EPSG:4326</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>本次範圍來源（官方資料衍生）</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>消防分隊與縣界範圍篩選及地圖定位。</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>由鄉鎮市區界聯集及簡化，不作法定界址依據。</t>
         </is>
@@ -15165,15 +15237,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>沿用舊版快取</t>
+          <t>2026-09-25（前次分析快取；本次查核官方版次）</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>本次僅沿用舊版GeoJSON（EPSG:4326）；原始數值檔座標系統未重新查核</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>前次成果對照；本次未重算</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>原複合災害報告的法定公告敏感區規劃參考範圍；本增補不重算該組統計。</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>官方註明數值範圍供規劃參考，實際法定範圍以公告圖資為準。</t>
         </is>
@@ -15202,15 +15284,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>沿用舊版快取</t>
+          <t>2026-09-25（前次分析快取）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>本次僅沿用舊版GeoJSON（EPSG:4326）；原檔名標示TWD97，未重新查核</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>前次成果對照；本次未重算</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>原複合災害報告的土石流影響範圍；本增補不重算該組統計。</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>潛勢影響範圍不代表災害必然發生。</t>
         </is>
@@ -15239,22 +15331,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>沿用舊版快取</t>
+          <t>2026-09-25（前次分析快取）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>本次僅沿用舊版GeoJSON（EPSG:4326）；原始檔座標系統未重新查核</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>前次成果對照；本次未重算</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>原複合災害報告的歷史淹水點；本增補不重算該組統計。</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>宜蘭子集無2023紀錄，且截至2025年度，不含2026年事件。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:I10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
